--- a/02_maestro/checkpoints/prueba_06_08/B01_trabajo.xlsx
+++ b/02_maestro/checkpoints/prueba_06_08/B01_trabajo.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -10755,7 +10755,7 @@
   <autoFilter ref="A1:K201"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Borrador,Sin borrador,Revisar_Juan,Enviado,Validado,Grabado"</formula1>
+      <formula1>"Borrador,Sin borrador,Por_revisar,Enviado,Validado,Grabado"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -27696,7 +27696,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Español redactado o adaptado por Claude (Revisar_Juan)</t>
+          <t>Español redactado o adaptado por Claude (Por_revisar)</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
